--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_10_R1.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_10_R1.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.5522</v>
+        <v>3.1887</v>
       </c>
       <c r="E2" t="n">
-        <v>2.8811</v>
+        <v>2.484</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6711</v>
+        <v>0.7047</v>
       </c>
       <c r="G2" t="n">
         <v>1.5295</v>
@@ -610,13 +610,13 @@
         <v>1.8556</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1129</v>
+        <v>-0.2506</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6018</v>
+        <v>0.2047</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4889</v>
+        <v>-0.4553</v>
       </c>
       <c r="V2" t="n">
         <v>1.214</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. NDIAYE</t>
+          <t>G. WATSON</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.4957</v>
+        <v>2.5322</v>
       </c>
       <c r="E3" t="n">
-        <v>4.2725</v>
+        <v>0.0143</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.7768</v>
+        <v>2.518</v>
       </c>
       <c r="G3" t="n">
-        <v>1.101</v>
+        <v>0.3141</v>
       </c>
       <c r="H3" t="n">
-        <v>1.8571</v>
+        <v>1.0838</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.7561</v>
+        <v>-0.7696</v>
       </c>
       <c r="J3" t="n">
-        <v>1.183</v>
+        <v>-0.508</v>
       </c>
       <c r="K3" t="n">
-        <v>1.1462</v>
+        <v>0.0476</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0368</v>
+        <v>-0.5556</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.082</v>
+        <v>0.8222</v>
       </c>
       <c r="N3" t="n">
-        <v>0.7109</v>
+        <v>1.0362</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.7929</v>
+        <v>-0.214</v>
       </c>
       <c r="P3" t="n">
-        <v>1.3917</v>
+        <v>2.5515</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.232</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.6237</v>
+        <v>2.5515</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8922</v>
+        <v>-1.4055</v>
       </c>
       <c r="T3" t="n">
-        <v>2.2492</v>
+        <v>-0.6917</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.357</v>
+        <v>-0.7139</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1107</v>
+        <v>1.0722</v>
       </c>
       <c r="W3" t="n">
-        <v>1.0722</v>
+        <v>1.214</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.9615</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. WATSON</t>
+          <t>M. NDIAYE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0365</v>
+        <v>2.3155</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.4143</v>
+        <v>2.8571</v>
       </c>
       <c r="F4" t="n">
-        <v>2.4508</v>
+        <v>-0.5415</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3141</v>
+        <v>1.101</v>
       </c>
       <c r="H4" t="n">
-        <v>1.0838</v>
+        <v>1.8571</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.7696</v>
+        <v>-0.7561</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.508</v>
+        <v>1.183</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0476</v>
+        <v>1.1462</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.5556</v>
+        <v>0.0368</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8222</v>
+        <v>-0.082</v>
       </c>
       <c r="N4" t="n">
-        <v>1.0362</v>
+        <v>0.7109</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.214</v>
+        <v>-0.7929</v>
       </c>
       <c r="P4" t="n">
-        <v>2.5515</v>
+        <v>1.3917</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0.232</v>
       </c>
       <c r="R4" t="n">
-        <v>2.5515</v>
+        <v>1.6237</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.9013</v>
+        <v>-0.288</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.1202</v>
+        <v>0.8338</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.7811</v>
+        <v>-1.1217</v>
       </c>
       <c r="V4" t="n">
+        <v>0.1107</v>
+      </c>
+      <c r="W4" t="n">
         <v>1.0722</v>
       </c>
-      <c r="W4" t="n">
-        <v>1.214</v>
-      </c>
       <c r="X4" t="n">
-        <v>-0.1418</v>
+        <v>-0.9615</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. LIGHTY</t>
+          <t>N. DE COLO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9265</v>
+        <v>0.968</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8625</v>
+        <v>2.0954</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0641</v>
+        <v>-1.1274</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4985</v>
+        <v>4.643</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7226</v>
+        <v>3.2713</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2241</v>
+        <v>1.3717</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7913</v>
+        <v>5.0643</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3263</v>
+        <v>2.7392</v>
       </c>
       <c r="L5" t="n">
-        <v>0.465</v>
+        <v>2.3251</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2928</v>
+        <v>-0.4214</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3963</v>
+        <v>0.5321</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6891</v>
+        <v>-0.9534</v>
       </c>
       <c r="P5" t="n">
-        <v>1.6237</v>
+        <v>-2.3195</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.232</v>
+        <v>-3.4793</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8556</v>
+        <v>1.1598</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.0539</v>
+        <v>-1.3555</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3031</v>
+        <v>-0.5619</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.357</v>
+        <v>-0.7936</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1418</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8304</v>
+        <v>0.7704</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.9206</v>
+        <v>-2.1068</v>
       </c>
       <c r="F6" t="n">
-        <v>3.751</v>
+        <v>2.8773</v>
       </c>
       <c r="G6" t="n">
         <v>0.09569999999999999</v>
@@ -922,13 +922,13 @@
         <v>2.3195</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3708</v>
+        <v>-0.4307</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.4936</v>
+        <v>-0.6798</v>
       </c>
       <c r="U6" t="n">
-        <v>1.1229</v>
+        <v>0.2491</v>
       </c>
       <c r="V6" t="n">
         <v>-1.214</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>N. DE COLO</t>
+          <t>D. LIGHTY</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.152</v>
+        <v>0.4854</v>
       </c>
       <c r="E7" t="n">
-        <v>1.313</v>
+        <v>0.1862</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.161</v>
+        <v>0.2993</v>
       </c>
       <c r="G7" t="n">
-        <v>4.643</v>
+        <v>0.4985</v>
       </c>
       <c r="H7" t="n">
-        <v>3.2713</v>
+        <v>0.7226</v>
       </c>
       <c r="I7" t="n">
-        <v>1.3717</v>
+        <v>-0.2241</v>
       </c>
       <c r="J7" t="n">
-        <v>5.0643</v>
+        <v>0.7913</v>
       </c>
       <c r="K7" t="n">
-        <v>2.7392</v>
+        <v>0.3263</v>
       </c>
       <c r="L7" t="n">
-        <v>2.3251</v>
+        <v>0.465</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4214</v>
+        <v>-0.2928</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5321</v>
+        <v>0.3963</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.9534</v>
+        <v>-0.6891</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.3195</v>
+        <v>1.6237</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.4793</v>
+        <v>-0.232</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1598</v>
+        <v>1.8556</v>
       </c>
       <c r="S7" t="n">
-        <v>-2.1715</v>
+        <v>-1.4949</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.3443</v>
+        <v>-0.3732</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.8272</v>
+        <v>-1.1217</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
       <c r="W7" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.0722</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7212</v>
+        <v>-0.2351</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5017</v>
+        <v>-0.1165</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2195</v>
+        <v>-0.1187</v>
       </c>
       <c r="G8" t="n">
         <v>-0.6312</v>
@@ -1078,13 +1078,13 @@
         <v>1.6237</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.4818</v>
+        <v>-0.9957</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8215</v>
+        <v>-0.4362</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6603</v>
+        <v>-0.5594</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.7967</v>
+        <v>-0.9402</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.4224</v>
+        <v>-2.2298</v>
       </c>
       <c r="F9" t="n">
-        <v>1.6257</v>
+        <v>1.2896</v>
       </c>
       <c r="G9" t="n">
         <v>1.0905</v>
@@ -1156,13 +1156,13 @@
         <v>0.6959</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2636</v>
+        <v>-0.407</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8215</v>
+        <v>-0.6289</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5579</v>
+        <v>0.2219</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.3415</v>
+        <v>-1.1153</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9768</v>
+        <v>-0.7841</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3647</v>
+        <v>-0.3311</v>
       </c>
       <c r="G10" t="n">
         <v>-0.6062</v>
@@ -1234,13 +1234,13 @@
         <v>0.6959</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3589</v>
+        <v>-0.1327</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.224</v>
+        <v>-0.0314</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1349</v>
+        <v>-0.1013</v>
       </c>
       <c r="V10" t="n">
         <v>-1.0722</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.004</v>
+        <v>-3.3162</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.3476</v>
+        <v>-3.9623</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3436</v>
+        <v>0.6461</v>
       </c>
       <c r="G11" t="n">
         <v>-0.5849</v>
@@ -1312,13 +1312,13 @@
         <v>1.6237</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.3315</v>
+        <v>-0.6438</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4086</v>
+        <v>-0.0233</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.923</v>
+        <v>-0.6205000000000001</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.6402</v>
+        <v>-7.0436</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.5693</v>
+        <v>-7.1407</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.0709</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="G12" t="n">
         <v>-4.265</v>
@@ -1390,13 +1390,13 @@
         <v>1.3917</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.2154</v>
+        <v>-1.6188</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0455</v>
+        <v>-0.617</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.1698</v>
+        <v>-1.0018</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.510300000000001</v>
+        <v>-2.390199999999998</v>
       </c>
       <c r="E13" t="n">
-        <v>-9.823599999999999</v>
+        <v>-8.703199999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>6.313400000000001</v>
+        <v>6.3134</v>
       </c>
       <c r="G13" t="n">
         <v>3.185</v>
@@ -1441,7 +1441,7 @@
         <v>-3.4293</v>
       </c>
       <c r="J13" t="n">
-        <v>2.4322</v>
+        <v>2.432199999999999</v>
       </c>
       <c r="K13" t="n">
         <v>1.864499999999999</v>
@@ -1459,7 +1459,7 @@
         <v>-3.9969</v>
       </c>
       <c r="P13" t="n">
-        <v>3.4793</v>
+        <v>3.479299999999999</v>
       </c>
       <c r="Q13" t="n">
         <v>-13.9173</v>
@@ -1468,13 +1468,13 @@
         <v>17.3966</v>
       </c>
       <c r="S13" t="n">
-        <v>-10.1436</v>
+        <v>-9.023199999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-4.1251</v>
+        <v>-3.0049</v>
       </c>
       <c r="U13" t="n">
-        <v>-6.0184</v>
+        <v>-6.0182</v>
       </c>
       <c r="V13" t="n">
         <v>-0.03109999999999991</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.8974</v>
+        <v>5.7465</v>
       </c>
       <c r="E14" t="n">
-        <v>2.6389</v>
+        <v>2.7569</v>
       </c>
       <c r="F14" t="n">
-        <v>3.2585</v>
+        <v>2.9896</v>
       </c>
       <c r="G14" t="n">
         <v>3.9585</v>
@@ -1546,13 +1546,13 @@
         <v>1.6237</v>
       </c>
       <c r="S14" t="n">
-        <v>1.4207</v>
+        <v>1.2698</v>
       </c>
       <c r="T14" t="n">
-        <v>0.311</v>
+        <v>0.429</v>
       </c>
       <c r="U14" t="n">
-        <v>1.1097</v>
+        <v>0.8408</v>
       </c>
       <c r="V14" t="n">
         <v>1.214</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. PRADILLA</t>
+          <t>I. IROEGBU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.653</v>
+        <v>4.4814</v>
       </c>
       <c r="E15" t="n">
-        <v>0.994</v>
+        <v>4.1149</v>
       </c>
       <c r="F15" t="n">
-        <v>3.6589</v>
+        <v>0.3665</v>
       </c>
       <c r="G15" t="n">
-        <v>1.6517</v>
+        <v>2.0184</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6712</v>
+        <v>0.9376</v>
       </c>
       <c r="I15" t="n">
-        <v>0.9804</v>
+        <v>1.0808</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6083</v>
+        <v>2.5901</v>
       </c>
       <c r="K15" t="n">
-        <v>0.6218</v>
+        <v>0.8234</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.0134</v>
+        <v>1.7666</v>
       </c>
       <c r="M15" t="n">
-        <v>1.0433</v>
+        <v>-0.5717</v>
       </c>
       <c r="N15" t="n">
-        <v>0.0495</v>
+        <v>0.1141</v>
       </c>
       <c r="O15" t="n">
-        <v>0.9939</v>
+        <v>-0.6859</v>
       </c>
       <c r="P15" t="n">
         <v>0.6959</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1598</v>
+        <v>-0.232</v>
       </c>
       <c r="R15" t="n">
-        <v>1.8556</v>
+        <v>0.9278</v>
       </c>
       <c r="S15" t="n">
-        <v>2.3054</v>
+        <v>0.695</v>
       </c>
       <c r="T15" t="n">
-        <v>1.5454</v>
+        <v>0.5427</v>
       </c>
       <c r="U15" t="n">
-        <v>0.76</v>
+        <v>0.1522</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.214</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>N. REUVERS</t>
+          <t>D. THOMPSON</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.6452</v>
+        <v>3.724</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1499</v>
+        <v>1.9878</v>
       </c>
       <c r="F16" t="n">
-        <v>3.4954</v>
+        <v>1.7362</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1896</v>
+        <v>2.4491</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.7309</v>
+        <v>0.0935</v>
       </c>
       <c r="I16" t="n">
-        <v>1.9205</v>
+        <v>2.3555</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.3176</v>
+        <v>2.6672</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.4551</v>
+        <v>0.0441</v>
       </c>
       <c r="L16" t="n">
-        <v>1.1374</v>
+        <v>2.6231</v>
       </c>
       <c r="M16" t="n">
-        <v>0.5072</v>
+        <v>-0.2181</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2759</v>
+        <v>0.0495</v>
       </c>
       <c r="O16" t="n">
-        <v>0.7831</v>
+        <v>-0.2676</v>
       </c>
       <c r="P16" t="n">
-        <v>1.8556</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-2.5515</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8556</v>
+        <v>1.6237</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2443</v>
+        <v>0.7363</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8883</v>
+        <v>0.2638</v>
       </c>
       <c r="U16" t="n">
-        <v>1.1325</v>
+        <v>0.4725</v>
       </c>
       <c r="V16" t="n">
-        <v>1.3558</v>
+        <v>1.4665</v>
       </c>
       <c r="W16" t="n">
-        <v>1.3558</v>
+        <v>1.6083</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. THOMPSON</t>
+          <t>J. PRADILLA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.5066</v>
+        <v>3.6586</v>
       </c>
       <c r="E17" t="n">
-        <v>2.3416</v>
+        <v>-0.0675</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1649</v>
+        <v>3.7261</v>
       </c>
       <c r="G17" t="n">
-        <v>2.4491</v>
+        <v>1.6517</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0935</v>
+        <v>0.6712</v>
       </c>
       <c r="I17" t="n">
-        <v>2.3555</v>
+        <v>0.9804</v>
       </c>
       <c r="J17" t="n">
-        <v>2.6672</v>
+        <v>0.6083</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0441</v>
+        <v>0.6218</v>
       </c>
       <c r="L17" t="n">
-        <v>2.6231</v>
+        <v>-0.0134</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2181</v>
+        <v>1.0433</v>
       </c>
       <c r="N17" t="n">
         <v>0.0495</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.2676</v>
+        <v>0.9939</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.9278</v>
+        <v>0.6959</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.5515</v>
+        <v>-1.1598</v>
       </c>
       <c r="R17" t="n">
-        <v>1.6237</v>
+        <v>1.8556</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5188</v>
+        <v>1.3111</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6176</v>
+        <v>0.4839</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0988</v>
+        <v>0.8272</v>
       </c>
       <c r="V17" t="n">
-        <v>1.4665</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.6083</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>I. IROEGBU</t>
+          <t>N. REUVERS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.4205</v>
+        <v>3.6465</v>
       </c>
       <c r="E18" t="n">
-        <v>3.2892</v>
+        <v>0.6217</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1313</v>
+        <v>3.0249</v>
       </c>
       <c r="G18" t="n">
-        <v>2.0184</v>
+        <v>0.1896</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9376</v>
+        <v>-1.7309</v>
       </c>
       <c r="I18" t="n">
-        <v>1.0808</v>
+        <v>1.9205</v>
       </c>
       <c r="J18" t="n">
-        <v>2.5901</v>
+        <v>-0.3176</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8234</v>
+        <v>-1.4551</v>
       </c>
       <c r="L18" t="n">
-        <v>1.7666</v>
+        <v>1.1374</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.5717</v>
+        <v>0.5072</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1141</v>
+        <v>-0.2759</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.6859</v>
+        <v>0.7831</v>
       </c>
       <c r="P18" t="n">
-        <v>0.6959</v>
+        <v>1.8556</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.232</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9278</v>
+        <v>1.8556</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3659</v>
+        <v>0.2456</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2829</v>
+        <v>-0.4165</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.083</v>
+        <v>0.662</v>
       </c>
       <c r="V18" t="n">
-        <v>1.0722</v>
+        <v>1.3558</v>
       </c>
       <c r="W18" t="n">
-        <v>1.214</v>
+        <v>1.3558</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>3.3817</v>
+        <v>1.8331</v>
       </c>
       <c r="E19" t="n">
-        <v>4.2266</v>
+        <v>3.2829</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.8449</v>
+        <v>-1.4498</v>
       </c>
       <c r="G19" t="n">
         <v>1.8393</v>
@@ -1936,13 +1936,13 @@
         <v>0.6959</v>
       </c>
       <c r="S19" t="n">
-        <v>3.8465</v>
+        <v>2.298</v>
       </c>
       <c r="T19" t="n">
-        <v>2.4065</v>
+        <v>1.4629</v>
       </c>
       <c r="U19" t="n">
-        <v>1.44</v>
+        <v>0.8351</v>
       </c>
       <c r="V19" t="n">
         <v>-1.6083</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.0548</v>
+        <v>-1.1892</v>
       </c>
       <c r="E20" t="n">
         <v>-1.2344</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1796</v>
+        <v>0.0452</v>
       </c>
       <c r="G20" t="n">
         <v>-0.1788</v>
@@ -2014,13 +2014,13 @@
         <v>0.232</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0518</v>
+        <v>-0.08260000000000001</v>
       </c>
       <c r="T20" t="n">
         <v>-0.0747</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1265</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. DE LARREA</t>
+          <t>J. PUERTO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.7299</v>
+        <v>-2.0973</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.1519</v>
+        <v>-3.7625</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.578</v>
+        <v>1.6652</v>
       </c>
       <c r="G21" t="n">
-        <v>0.5931</v>
+        <v>-3.7813</v>
       </c>
       <c r="H21" t="n">
-        <v>0.312</v>
+        <v>0.1069</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2811</v>
+        <v>-3.8881</v>
       </c>
       <c r="J21" t="n">
-        <v>1.1225</v>
+        <v>-4.1208</v>
       </c>
       <c r="K21" t="n">
-        <v>1.0489</v>
+        <v>-0.4468</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0736</v>
+        <v>-3.6741</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.5294</v>
+        <v>0.3396</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.7369</v>
+        <v>0.5536</v>
       </c>
       <c r="O21" t="n">
-        <v>0.2075</v>
+        <v>-0.214</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.3195</v>
+        <v>0.6959</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.4793</v>
+        <v>-0.232</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1598</v>
+        <v>0.9278</v>
       </c>
       <c r="S21" t="n">
-        <v>1.8574</v>
+        <v>0.8463000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>1.9935</v>
+        <v>0.4485</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1362</v>
+        <v>0.3978</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.8608</v>
+        <v>0.1418</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.7886</v>
+        <v>0.1418</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. PUERTO</t>
+          <t>S. DE LARREA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.4449</v>
+        <v>-2.3703</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.942</v>
+        <v>-1.8596</v>
       </c>
       <c r="F22" t="n">
-        <v>1.4971</v>
+        <v>-0.5108</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.7813</v>
+        <v>0.5931</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1069</v>
+        <v>0.312</v>
       </c>
       <c r="I22" t="n">
-        <v>-3.8881</v>
+        <v>0.2811</v>
       </c>
       <c r="J22" t="n">
-        <v>-4.1208</v>
+        <v>1.1225</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.4468</v>
+        <v>1.0489</v>
       </c>
       <c r="L22" t="n">
-        <v>-3.6741</v>
+        <v>0.0736</v>
       </c>
       <c r="M22" t="n">
-        <v>0.3396</v>
+        <v>-0.5294</v>
       </c>
       <c r="N22" t="n">
-        <v>0.5536</v>
+        <v>-0.7369</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.214</v>
+        <v>0.2075</v>
       </c>
       <c r="P22" t="n">
-        <v>0.6959</v>
+        <v>-2.3195</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.232</v>
+        <v>-3.4793</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9278</v>
+        <v>1.1598</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5012</v>
+        <v>1.2169</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.731</v>
+        <v>1.2858</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2298</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="V22" t="n">
-        <v>0.1418</v>
+        <v>-1.8608</v>
       </c>
       <c r="W22" t="n">
-        <v>0.1418</v>
+        <v>-0.7886</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.152</v>
+        <v>-4.1184</v>
       </c>
       <c r="E23" t="n">
         <v>-3.4346</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.7174</v>
+        <v>-0.6838</v>
       </c>
       <c r="G23" t="n">
         <v>-5.9044</v>
@@ -2248,13 +2248,13 @@
         <v>0.9278</v>
       </c>
       <c r="S23" t="n">
-        <v>0.8246</v>
+        <v>0.8582</v>
       </c>
       <c r="T23" t="n">
         <v>1.2151</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3905</v>
+        <v>-0.3569</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>N. SAKO</t>
+          <t>K. TAYLOR</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.1566</v>
+        <v>-4.2269</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.9986</v>
+        <v>-5.3663</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.158</v>
+        <v>1.1394</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.2203</v>
+        <v>-2.7998</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.5043</v>
+        <v>-3.1679</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.716</v>
+        <v>0.368</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.2518</v>
+        <v>-1.9738</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.3254</v>
+        <v>-2.2414</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0736</v>
+        <v>0.2676</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.9684</v>
+        <v>-0.826</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.1788</v>
+        <v>-0.9265</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.7896</v>
+        <v>0.1005</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.1598</v>
+        <v>-1.6237</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.3917</v>
+        <v>-3.4793</v>
       </c>
       <c r="R24" t="n">
-        <v>0.232</v>
+        <v>1.8556</v>
       </c>
       <c r="S24" t="n">
-        <v>0.9735</v>
+        <v>0.1966</v>
       </c>
       <c r="T24" t="n">
-        <v>0.6449</v>
+        <v>0.0868</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3286</v>
+        <v>0.1098</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.7501</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.7501</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>K. TAYLOR</t>
+          <t>N. SAKO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.4559</v>
+        <v>-5.5777</v>
       </c>
       <c r="E25" t="n">
-        <v>-6.192</v>
+        <v>-3.3525</v>
       </c>
       <c r="F25" t="n">
-        <v>0.7362</v>
+        <v>-2.2252</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.7998</v>
+        <v>-3.2203</v>
       </c>
       <c r="H25" t="n">
-        <v>-3.1679</v>
+        <v>-2.5043</v>
       </c>
       <c r="I25" t="n">
-        <v>0.368</v>
+        <v>-0.716</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.9738</v>
+        <v>-2.2518</v>
       </c>
       <c r="K25" t="n">
-        <v>-2.2414</v>
+        <v>-2.3254</v>
       </c>
       <c r="L25" t="n">
-        <v>0.2676</v>
+        <v>0.0736</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.826</v>
+        <v>-0.9684</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.9265</v>
+        <v>-0.1788</v>
       </c>
       <c r="O25" t="n">
-        <v>0.1005</v>
+        <v>-0.7896</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.6237</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q25" t="n">
-        <v>-3.4793</v>
+        <v>-1.3917</v>
       </c>
       <c r="R25" t="n">
-        <v>1.8556</v>
+        <v>0.232</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.0324</v>
+        <v>0.5524</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.7389</v>
+        <v>0.291</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.2934</v>
+        <v>0.2614</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>-1.7501</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>-1.7501</v>
       </c>
     </row>
     <row r="26">
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>3.510299999999994</v>
+        <v>3.510300000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>-6.313299999999999</v>
+        <v>-6.3132</v>
       </c>
       <c r="F26" t="n">
-        <v>9.823600000000001</v>
+        <v>9.823499999999999</v>
       </c>
       <c r="G26" t="n">
         <v>-3.1849</v>
@@ -2452,16 +2452,16 @@
         <v>-6.6142</v>
       </c>
       <c r="I26" t="n">
-        <v>3.429199999999999</v>
+        <v>3.4292</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.7526000000000017</v>
+        <v>-0.7525999999999999</v>
       </c>
       <c r="K26" t="n">
         <v>-4.7498</v>
       </c>
       <c r="L26" t="n">
-        <v>3.997000000000001</v>
+        <v>3.996999999999999</v>
       </c>
       <c r="M26" t="n">
         <v>-2.4322</v>
@@ -2470,7 +2470,7 @@
         <v>-1.8645</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.5676999999999998</v>
+        <v>-0.5677</v>
       </c>
       <c r="P26" t="n">
         <v>-3.4793</v>
@@ -2482,19 +2482,19 @@
         <v>13.9173</v>
       </c>
       <c r="S26" t="n">
-        <v>10.1435</v>
+        <v>10.1436</v>
       </c>
       <c r="T26" t="n">
-        <v>6.018199999999999</v>
+        <v>6.018300000000002</v>
       </c>
       <c r="U26" t="n">
-        <v>4.1252</v>
+        <v>4.125</v>
       </c>
       <c r="V26" t="n">
-        <v>0.03109999999999968</v>
+        <v>0.03109999999999991</v>
       </c>
       <c r="W26" t="n">
-        <v>5.817500000000001</v>
+        <v>5.8175</v>
       </c>
       <c r="X26" t="n">
         <v>-5.7864</v>
